--- a/output/pdf_financials_xlsx/GT.xlsx
+++ b/output/pdf_financials_xlsx/GT.xlsx
@@ -6095,34 +6095,34 @@
         <v>0.166758</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.166758</v>
+        <v>0.290168</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.558188</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.644285</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.707054</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.308542</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.054316</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.577509</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.060107</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.981276</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.204844</v>
       </c>
     </row>
     <row r="93">
@@ -10023,7 +10023,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11223,7 +11227,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11837,7 +11845,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12449,7 +12461,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13542,7 +13558,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14445,7 +14465,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -15055,7 +15079,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GT.xlsx
+++ b/output/pdf_financials_xlsx/GT.xlsx
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.060858</v>
+        <v>0.461531</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.05566</v>
@@ -975,19 +975,19 @@
         <v>1.682453</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.482071</v>
+        <v>11.190812</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.529819</v>
+        <v>10.073211</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.478448</v>
+        <v>10.546695</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.406088</v>
+        <v>4.572169</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.222192</v>
+        <v>2.169062</v>
       </c>
     </row>
     <row r="11">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.060858</v>
+        <v>-0.461531</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -1041,19 +1041,19 @@
         <v>-1.682453</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.482071</v>
+        <v>-11.190812</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.529819</v>
+        <v>-10.073211</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.478448</v>
+        <v>-10.546695</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.406088</v>
+        <v>-4.572169</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.222192</v>
+        <v>-2.169062</v>
       </c>
     </row>
     <row r="12">
@@ -1077,43 +1077,43 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000625</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004164</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002771</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001233</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001424</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001605</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001737</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.103794</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.239939</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.625493</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.507335</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.260479</v>
       </c>
     </row>
     <row r="13">
@@ -2049,43 +2049,43 @@
         <v>-0.030217</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.036791</v>
+        <v>-0.037416</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.060579</v>
+        <v>-0.06474299999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.062623</v>
+        <v>-0.06539399999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.093168</v>
+        <v>-0.094401</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.938684</v>
+        <v>-2.940108</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.6252450000000001</v>
+        <v>-0.62685</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.868908</v>
+        <v>-0.870645</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.570943</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.682927</v>
+        <v>-10.786721</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-8.009886</v>
+        <v>-8.249825</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-7.996396</v>
+        <v>-8.621888999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.841965</v>
+        <v>-3.3493</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.82744</v>
+        <v>-2.087919</v>
       </c>
     </row>
     <row r="28">
@@ -2169,43 +2169,43 @@
         <v>-0.030217</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.036791</v>
+        <v>-0.037416</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.060579</v>
+        <v>-0.06474299999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.062623</v>
+        <v>-0.06539399999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.093168</v>
+        <v>-0.094401</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.938684</v>
+        <v>-2.940108</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.6252450000000001</v>
+        <v>-0.62685</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.868684</v>
+        <v>-0.870421</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.570308</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.682927</v>
+        <v>-10.786721</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-8.009886</v>
+        <v>-8.249825</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.996396</v>
+        <v>-8.621888999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.841965</v>
+        <v>-3.3493</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.82744</v>
+        <v>-2.087919</v>
       </c>
     </row>
     <row r="30">
@@ -2477,46 +2477,46 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002762</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005274</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002352</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001041</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000746</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.037048</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001022</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.780176</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>15.060023</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>11.388062</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>10.669641</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>9.128391000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>7.504507</v>
       </c>
     </row>
     <row r="35">
@@ -2597,46 +2597,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002762</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005274</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002352</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001041</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000746</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.037048</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001022</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.780176</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>15.060023</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>11.388062</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.052</v>
+        <v>10.721641</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.052</v>
+        <v>9.180391</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.021785</v>
+        <v>7.526292</v>
       </c>
     </row>
     <row r="37">
@@ -3317,46 +3317,46 @@
         <v>0.012284</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.004012</v>
+        <v>0.00125</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.006524</v>
+        <v>0.00125</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001326</v>
+        <v>0.00125</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.028074</v>
+        <v>0.027033</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.164667</v>
+        <v>0.163921</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.046683</v>
+        <v>0.009634999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.025425</v>
+        <v>0.024403</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.854801</v>
+        <v>0.074625</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>15.690394</v>
+        <v>0.630371</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>12.023085</v>
+        <v>0.635023</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>11.154493</v>
+        <v>0.484852</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>9.259653999999999</v>
+        <v>0.131263</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>7.611123</v>
+        <v>0.106616</v>
       </c>
     </row>
     <row r="49">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9423,7 +9423,11 @@
           <t>Reclamation deposits 16</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10724,7 +10728,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -15382,7 +15390,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -19133,7 +19141,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -31148,7 +31156,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -52825,7 +52837,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -52889,19 +52901,19 @@
         </is>
       </c>
       <c r="Q438" s="5" t="n">
-        <v>-11.190812</v>
+        <v>11.190812</v>
       </c>
       <c r="R438" s="5" t="n">
-        <v>-10.073211</v>
+        <v>10.073211</v>
       </c>
       <c r="S438" s="5" t="n">
-        <v>-10.546695</v>
+        <v>10.546695</v>
       </c>
       <c r="T438" s="5" t="n">
-        <v>-4.572169</v>
+        <v>4.572169</v>
       </c>
       <c r="U438" s="5" t="n">
-        <v>-2.169062</v>
+        <v>2.169062</v>
       </c>
     </row>
     <row r="439">
@@ -53122,7 +53134,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -56108,7 +56120,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -57607,7 +57619,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -58597,7 +58609,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -60070,7 +60082,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -60169,7 +60181,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -64080,7 +64092,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">

--- a/output/pdf_financials_xlsx/GT.xlsx
+++ b/output/pdf_financials_xlsx/GT.xlsx
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.04825</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -47686,7 +47686,11 @@
           <t>Issuance of common shares, net of issuance costs (note 7(b))</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -49318,7 +49322,11 @@
           <t>Issuance of common shares, net of issuance costs (note 7(b))</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GT.xlsx
+++ b/output/pdf_financials_xlsx/GT.xlsx
@@ -4534,25 +4534,25 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.016862</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.192997</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.412232</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.237149</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.112027</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.021086</v>
       </c>
     </row>
     <row r="68">
@@ -6582,19 +6582,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00241</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005378</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.002666</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.003319</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001347</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
@@ -6885,13 +6885,13 @@
         <v>-0.017522</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.006985</v>
+        <v>0.001607</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.042934</v>
+        <v>0.0456</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.014572</v>
+        <v>-0.011253</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-0.023836</v>
@@ -7209,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003049</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003049</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8685,7 +8685,7 @@
         <v>-1.313328</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-11.527177</v>
+        <v>-11.530226</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-8.270113</v>
@@ -31261,7 +31261,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -35695,7 +35699,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -39010,7 +39018,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -46072,7 +46084,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -48609,7 +48625,11 @@
           <t>Increase in HST receivable</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -61373,7 +61393,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
